--- a/output/Tables/Sensitivity analyses/HIA_DRF_sensitivity_1000replicate.xlsx
+++ b/output/Tables/Sensitivity analyses/HIA_DRF_sensitivity_1000replicate.xlsx
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>2564.803</v>
+        <v>2564.839</v>
       </c>
       <c r="C3">
-        <v>2380.83</v>
+        <v>2381.799</v>
       </c>
       <c r="D3">
-        <v>2755.511</v>
+        <v>2756.768</v>
       </c>
       <c r="E3">
-        <v>4318.025000000001</v>
+        <v>4318.133</v>
       </c>
       <c r="F3">
-        <v>3973.082999999999</v>
+        <v>3970.713</v>
       </c>
       <c r="G3">
-        <v>4685.461</v>
+        <v>4686.567</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>2137.31</v>
+        <v>2137.236</v>
       </c>
       <c r="C4">
-        <v>2033.694</v>
+        <v>2033.675</v>
       </c>
       <c r="D4">
-        <v>2243.612</v>
+        <v>2243.339</v>
       </c>
       <c r="E4">
-        <v>2635.237000000001</v>
+        <v>2635.507000000001</v>
       </c>
       <c r="F4">
-        <v>2525.373000000001</v>
+        <v>2524.905</v>
       </c>
       <c r="G4">
-        <v>2750.039</v>
+        <v>2750.237</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>41046.082</v>
+        <v>41047.704</v>
       </c>
       <c r="C5">
-        <v>39442.96000000001</v>
+        <v>39443.488</v>
       </c>
       <c r="D5">
-        <v>42646.372</v>
+        <v>42659.98</v>
       </c>
       <c r="E5">
-        <v>36614.698</v>
+        <v>36619.72099999999</v>
       </c>
       <c r="F5">
-        <v>35353.686</v>
+        <v>35349.97199999999</v>
       </c>
       <c r="G5">
-        <v>37888.324</v>
+        <v>37897.425</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>13374.153</v>
+        <v>13374.952</v>
       </c>
       <c r="C6">
-        <v>12985.454</v>
+        <v>12986.887</v>
       </c>
       <c r="D6">
-        <v>13764.361</v>
+        <v>13764.627</v>
       </c>
       <c r="E6">
-        <v>26078.447</v>
+        <v>26079.172</v>
       </c>
       <c r="F6">
-        <v>25294.498</v>
+        <v>25300.53999999999</v>
       </c>
       <c r="G6">
-        <v>26874.687</v>
+        <v>26868.49799999999</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>6948.271000000001</v>
+        <v>6948.093999999999</v>
       </c>
       <c r="C7">
-        <v>6541.331</v>
+        <v>6541.084999999999</v>
       </c>
       <c r="D7">
-        <v>7364.609</v>
+        <v>7361.279</v>
       </c>
       <c r="E7">
-        <v>11722.369</v>
+        <v>11721.661</v>
       </c>
       <c r="F7">
-        <v>11175.915</v>
+        <v>11178.246</v>
       </c>
       <c r="G7">
-        <v>12279.226</v>
+        <v>12280.096</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>240946.958</v>
+        <v>224418.856</v>
       </c>
       <c r="C8">
-        <v>234710.546</v>
+        <v>218479.514</v>
       </c>
       <c r="D8">
-        <v>247203.2469999999</v>
+        <v>230356.4469999999</v>
       </c>
       <c r="E8">
-        <v>77759.21100000001</v>
+        <v>72400.62299999999</v>
       </c>
       <c r="F8">
-        <v>74882.989</v>
+        <v>69674.46400000001</v>
       </c>
       <c r="G8">
-        <v>80671.29799999998</v>
+        <v>75196.823</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>307017.577</v>
+        <v>290491.681</v>
       </c>
       <c r="C9">
-        <v>298094.815</v>
+        <v>281866.448</v>
       </c>
       <c r="D9">
-        <v>315977.7119999999</v>
+        <v>299142.4399999999</v>
       </c>
       <c r="E9">
-        <v>159127.987</v>
+        <v>153774.817</v>
       </c>
       <c r="F9">
-        <v>153205.544</v>
+        <v>147998.84</v>
       </c>
       <c r="G9">
-        <v>165149.035</v>
+        <v>159679.646</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
-        <v>326288.249</v>
+        <v>309762.353</v>
       </c>
       <c r="C10">
-        <v>316405.065</v>
+        <v>300176.698</v>
       </c>
       <c r="D10">
-        <v>336219.6069999999</v>
+        <v>319384.3349999999</v>
       </c>
       <c r="E10">
-        <v>361991.983</v>
+        <v>356638.813</v>
       </c>
       <c r="F10">
-        <v>349748.616</v>
+        <v>344541.9119999999</v>
       </c>
       <c r="G10">
-        <v>374358.7289999999</v>
+        <v>368889.34</v>
       </c>
     </row>
   </sheetData>
